--- a/salidas/empresas/GOOGL.xlsx
+++ b/salidas/empresas/GOOGL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>10.72526836395264</v>
+        <v>10.72526741027832</v>
       </c>
       <c r="C2" t="n">
         <v>10.82732677459717</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>8.989038467407227</v>
+        <v>8.989039421081543</v>
       </c>
       <c r="C3" t="n">
         <v>9.074575424194336</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>9.667763710021973</v>
+        <v>9.667764663696289</v>
       </c>
       <c r="C4" t="n">
         <v>9.759759902954102</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>10.36037254333496</v>
+        <v>10.36037349700928</v>
       </c>
       <c r="C5" t="n">
         <v>10.45895862579346</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>9.217097282409668</v>
+        <v>9.217098236083984</v>
       </c>
       <c r="C6" t="n">
         <v>9.304804801940918</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>10.39482975006104</v>
+        <v>10.39482879638672</v>
       </c>
       <c r="C7" t="n">
         <v>10.49374389648438</v>
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>9.383431434631348</v>
+        <v>9.383434295654297</v>
       </c>
       <c r="C9" t="n">
         <v>9.472723007202148</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>9.962756156921387</v>
+        <v>9.962754249572754</v>
       </c>
       <c r="C10" t="n">
         <v>10.05755805969238</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>11.80929851531982</v>
+        <v>11.80929756164551</v>
       </c>
       <c r="C11" t="n">
         <v>11.92167186737061</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>11.41490459442139</v>
+        <v>11.41490364074707</v>
       </c>
       <c r="C13" t="n">
         <v>11.52352428436279</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.43175220489502</v>
+        <v>12.43175315856934</v>
       </c>
       <c r="C14" t="n">
         <v>12.55004978179932</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>11.14147853851318</v>
+        <v>11.14147758483887</v>
       </c>
       <c r="C15" t="n">
         <v>11.24749660491943</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>11.35739135742188</v>
+        <v>11.35739231109619</v>
       </c>
       <c r="C16" t="n">
         <v>11.46546459197998</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>11.68510341644287</v>
+        <v>11.68510437011719</v>
       </c>
       <c r="C17" t="n">
         <v>11.79629611968994</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>12.34276008605957</v>
+        <v>12.3427619934082</v>
       </c>
       <c r="C18" t="n">
         <v>12.46020984649658</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>12.64246082305908</v>
+        <v>12.64245986938477</v>
       </c>
       <c r="C20" t="n">
         <v>12.76276302337646</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>12.77260589599609</v>
+        <v>12.77260398864746</v>
       </c>
       <c r="C21" t="n">
         <v>12.89414405822754</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>14.06213569641113</v>
+        <v>14.06213474273682</v>
       </c>
       <c r="C22" t="n">
         <v>14.19594573974609</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>17.52592277526855</v>
+        <v>17.52592468261719</v>
       </c>
       <c r="C23" t="n">
         <v>17.69269371032715</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>17.14119338989258</v>
+        <v>17.14119529724121</v>
       </c>
       <c r="C25" t="n">
         <v>17.3043041229248</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>13.98851108551025</v>
+        <v>13.98851013183594</v>
       </c>
       <c r="C26" t="n">
         <v>14.12162208557129</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>10.91887283325195</v>
+        <v>10.91887187957764</v>
       </c>
       <c r="C28" t="n">
         <v>11.02277278900146</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>14.23615550994873</v>
+        <v>14.23615646362305</v>
       </c>
       <c r="C29" t="n">
         <v>14.37162208557129</v>
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>11.4845609664917</v>
+        <v>11.48456001281738</v>
       </c>
       <c r="C33" t="n">
         <v>11.59384441375732</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>9.928546905517578</v>
+        <v>9.928545951843262</v>
       </c>
       <c r="C34" t="n">
         <v>10.02302265167236</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>8.908225059509277</v>
+        <v>8.908226013183594</v>
       </c>
       <c r="C35" t="n">
         <v>8.992993354797363</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>7.626379013061523</v>
+        <v>7.626378536224365</v>
       </c>
       <c r="C37" t="n">
         <v>7.698948860168457</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>8.391866683959961</v>
+        <v>8.391867637634277</v>
       </c>
       <c r="C38" t="n">
         <v>8.471721649169922</v>
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>8.628108978271484</v>
+        <v>8.628108024597168</v>
       </c>
       <c r="C40" t="n">
         <v>8.710209846496582</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>9.815754890441895</v>
+        <v>9.815755844116211</v>
       </c>
       <c r="C41" t="n">
         <v>9.909158706665039</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>11.44440078735352</v>
+        <v>11.4443998336792</v>
       </c>
       <c r="C45" t="n">
         <v>11.55330276489258</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>12.29169464111328</v>
+        <v>12.29169654846191</v>
       </c>
       <c r="C46" t="n">
         <v>12.40865898132324</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>13.28995418548584</v>
+        <v>13.28995323181152</v>
       </c>
       <c r="C47" t="n">
         <v>13.41641616821289</v>
@@ -1374,7 +1386,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>15.36876964569092</v>
+        <v>15.36877059936523</v>
       </c>
       <c r="C49" t="n">
         <v>15.5150146484375</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>13.13675594329834</v>
+        <v>13.13675689697266</v>
       </c>
       <c r="C50" t="n">
         <v>13.26176166534424</v>
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>14.05841541290283</v>
+        <v>14.05841636657715</v>
       </c>
       <c r="C52" t="n">
         <v>14.19219207763672</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>13.03165054321289</v>
+        <v>13.03165149688721</v>
       </c>
       <c r="C53" t="n">
         <v>13.15565586090088</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>12.03835010528564</v>
+        <v>12.03834819793701</v>
       </c>
       <c r="C54" t="n">
         <v>12.15290260314941</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>11.02992820739746</v>
+        <v>11.02992630004883</v>
       </c>
       <c r="C55" t="n">
         <v>11.13488483428955</v>
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1599,7 +1611,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>13.03388023376465</v>
+        <v>13.03388118743896</v>
       </c>
       <c r="C58" t="n">
         <v>13.15790843963623</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>15.21309471130371</v>
+        <v>15.21309566497803</v>
       </c>
       <c r="C59" t="n">
         <v>15.3578577041626</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>13.77557373046875</v>
+        <v>13.77557468414307</v>
       </c>
       <c r="C60" t="n">
         <v>13.90665721893311</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>14.72400379180908</v>
+        <v>14.72400569915771</v>
       </c>
       <c r="C61" t="n">
         <v>14.86411380767822</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>14.88240814208984</v>
+        <v>14.88240718841553</v>
       </c>
       <c r="C62" t="n">
         <v>15.02402400970459</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>15.20565891265869</v>
+        <v>15.20565795898438</v>
       </c>
       <c r="C63" t="n">
         <v>15.35035037994385</v>
@@ -1778,7 +1790,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>13.48777103424072</v>
+        <v>13.48777198791504</v>
       </c>
       <c r="C65" t="n">
         <v>13.61611557006836</v>
@@ -1836,7 +1848,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>12.55272388458252</v>
+        <v>12.5527229309082</v>
       </c>
       <c r="C67" t="n">
         <v>12.6721715927124</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>14.9649543762207</v>
+        <v>14.96495532989502</v>
       </c>
       <c r="C68" t="n">
         <v>15.10735702514648</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>13.40993309020996</v>
+        <v>13.40993213653564</v>
       </c>
       <c r="C69" t="n">
         <v>13.53753757476807</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>12.76739692687988</v>
+        <v>12.76739883422852</v>
       </c>
       <c r="C70" t="n">
         <v>12.88888931274414</v>
@@ -1981,7 +1993,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>14.85836124420166</v>
+        <v>14.85836219787598</v>
       </c>
       <c r="C72" t="n">
         <v>14.9997501373291</v>
@@ -2039,7 +2051,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>14.38042831420898</v>
+        <v>14.38042736053467</v>
       </c>
       <c r="C74" t="n">
         <v>14.51726722717285</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>15.32588672637939</v>
+        <v>15.32588481903076</v>
       </c>
       <c r="C75" t="n">
         <v>15.47172164916992</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>15.89578628540039</v>
+        <v>15.89578723907471</v>
       </c>
       <c r="C76" t="n">
         <v>16.04704666137695</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>14.99370956420898</v>
+        <v>14.99371147155762</v>
       </c>
       <c r="C77" t="n">
         <v>15.13638591766357</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>14.39901828765869</v>
+        <v>14.39901924133301</v>
       </c>
       <c r="C78" t="n">
         <v>14.53603553771973</v>
@@ -2213,7 +2225,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>15.69078063964844</v>
+        <v>15.69078159332275</v>
       </c>
       <c r="C80" t="n">
         <v>15.84008979797363</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>16.98278999328613</v>
+        <v>16.98279190063477</v>
       </c>
       <c r="C81" t="n">
         <v>17.14439392089844</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>18.70340728759766</v>
+        <v>18.70340538024902</v>
       </c>
       <c r="C82" t="n">
         <v>18.88138008117676</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>16.86404800415039</v>
+        <v>16.86405181884766</v>
       </c>
       <c r="C83" t="n">
         <v>17.0245246887207</v>
@@ -2358,7 +2370,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2387,7 +2399,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>18.73290634155273</v>
+        <v>18.7329044342041</v>
       </c>
       <c r="C86" t="n">
         <v>18.91116142272949</v>
@@ -2445,7 +2457,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>19.68728446960449</v>
+        <v>19.68728637695312</v>
       </c>
       <c r="C88" t="n">
         <v>19.87462425231934</v>
@@ -2503,7 +2515,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>21.5967903137207</v>
+        <v>21.59679222106934</v>
       </c>
       <c r="C90" t="n">
         <v>21.80230140686035</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>21.82361030578613</v>
+        <v>21.82361793518066</v>
       </c>
       <c r="C91" t="n">
         <v>22.03128051757812</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>22.00655937194824</v>
+        <v>22.00655746459961</v>
       </c>
       <c r="C92" t="n">
         <v>22.21596527099609</v>
@@ -2619,7 +2631,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>21.71305274963379</v>
+        <v>21.71305465698242</v>
       </c>
       <c r="C94" t="n">
         <v>21.91967010498047</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>25.54719161987305</v>
+        <v>25.54718971252441</v>
       </c>
       <c r="C95" t="n">
         <v>25.79029083251953</v>
@@ -2706,7 +2718,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>27.78143310546875</v>
+        <v>27.78143692016602</v>
       </c>
       <c r="C97" t="n">
         <v>28.04579544067383</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>29.27523231506348</v>
+        <v>29.27522850036621</v>
       </c>
       <c r="C98" t="n">
         <v>29.55380439758301</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>30.13491821289062</v>
+        <v>30.13492012023926</v>
       </c>
       <c r="C99" t="n">
         <v>30.42167282104492</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>27.62774276733398</v>
+        <v>27.62774085998535</v>
       </c>
       <c r="C100" t="n">
         <v>27.89064025878906</v>
@@ -2851,7 +2863,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>28.31307601928711</v>
+        <v>28.31307983398438</v>
       </c>
       <c r="C102" t="n">
         <v>28.58250045776367</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>28.95794677734375</v>
+        <v>28.95794486999512</v>
       </c>
       <c r="C103" t="n">
         <v>29.23349952697754</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>28.70436096191406</v>
+        <v>28.70435905456543</v>
       </c>
       <c r="C104" t="n">
         <v>28.97750091552734</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>28.84353256225586</v>
+        <v>28.84353446960449</v>
       </c>
       <c r="C105" t="n">
         <v>29.11800003051758</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>29.1431827545166</v>
+        <v>29.14317893981934</v>
       </c>
       <c r="C106" t="n">
         <v>29.42049980163574</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>28.12586212158203</v>
+        <v>28.12586402893066</v>
       </c>
       <c r="C107" t="n">
         <v>28.39349937438965</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>27.19521903991699</v>
+        <v>27.19522094726562</v>
       </c>
       <c r="C108" t="n">
         <v>27.45400047302246</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>26.28289794921875</v>
+        <v>26.28289985656738</v>
       </c>
       <c r="C109" t="n">
         <v>26.53300094604492</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>26.62415313720703</v>
+        <v>26.62415504455566</v>
       </c>
       <c r="C110" t="n">
         <v>26.87750053405762</v>
@@ -3141,7 +3153,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3170,7 +3182,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3199,7 +3211,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>27.00899314880371</v>
+        <v>27.00899124145508</v>
       </c>
       <c r="C114" t="n">
         <v>27.26600074768066</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>26.74748229980469</v>
+        <v>26.74748039245605</v>
       </c>
       <c r="C115" t="n">
         <v>27.00200080871582</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>32.56512451171875</v>
+        <v>32.56512069702148</v>
       </c>
       <c r="C116" t="n">
         <v>32.875</v>
@@ -3315,7 +3327,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>31.61763763427734</v>
+        <v>31.61763572692871</v>
       </c>
       <c r="C118" t="n">
         <v>31.91850090026855</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>36.52196884155273</v>
+        <v>36.52196502685547</v>
       </c>
       <c r="C119" t="n">
         <v>36.86949920654297</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>37.78296661376953</v>
+        <v>37.78297805786133</v>
       </c>
       <c r="C120" t="n">
         <v>38.14250183105469</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>38.53382110595703</v>
+        <v>38.53383255004883</v>
       </c>
       <c r="C121" t="n">
         <v>38.9005012512207</v>
@@ -3450,11 +3462,11 @@
       <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>37.70867919921875</v>
+        <v>37.70867156982422</v>
       </c>
       <c r="C122" t="n">
         <v>38.06750106811523</v>
@@ -3469,11 +3481,11 @@
       <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>35.52296829223633</v>
+        <v>35.52297210693359</v>
       </c>
       <c r="C123" t="n">
         <v>35.86100006103516</v>
@@ -3494,11 +3506,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>37.78544998168945</v>
+        <v>37.78544616699219</v>
       </c>
       <c r="C124" t="n">
         <v>38.14500045776367</v>
@@ -3519,11 +3531,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>35.06037521362305</v>
+        <v>35.06038284301758</v>
       </c>
       <c r="C125" t="n">
         <v>35.39400100708008</v>
@@ -3544,11 +3556,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>37.08956527709961</v>
+        <v>37.08956909179688</v>
       </c>
       <c r="C126" t="n">
         <v>37.44250106811523</v>
@@ -3569,11 +3581,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>34.84492492675781</v>
+        <v>34.84492111206055</v>
       </c>
       <c r="C127" t="n">
         <v>35.17649841308594</v>
@@ -3594,11 +3606,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>39.19404983520508</v>
+        <v>39.19404220581055</v>
       </c>
       <c r="C128" t="n">
         <v>39.56700134277344</v>
@@ -3619,7 +3631,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3644,11 +3656,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>39.82405090332031</v>
+        <v>39.82404327392578</v>
       </c>
       <c r="C130" t="n">
         <v>40.20299911499023</v>
@@ -3669,11 +3681,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>40.1132926940918</v>
+        <v>40.11329650878906</v>
       </c>
       <c r="C131" t="n">
         <v>40.49499893188477</v>
@@ -3694,11 +3706,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>38.42832946777344</v>
+        <v>38.4283332824707</v>
       </c>
       <c r="C132" t="n">
         <v>38.79399871826172</v>
@@ -3719,7 +3731,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3744,7 +3756,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3769,11 +3781,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>41.84828567504883</v>
+        <v>41.8482780456543</v>
       </c>
       <c r="C135" t="n">
         <v>42.24649810791016</v>
@@ -3794,11 +3806,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>41.99042510986328</v>
+        <v>41.99043273925781</v>
       </c>
       <c r="C136" t="n">
         <v>42.38999938964844</v>
@@ -3819,11 +3831,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>45.79027557373047</v>
+        <v>45.7902717590332</v>
       </c>
       <c r="C137" t="n">
         <v>46.22600173950195</v>
@@ -3844,11 +3856,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>48.8892822265625</v>
+        <v>48.88928604125977</v>
       </c>
       <c r="C138" t="n">
         <v>49.35449981689453</v>
@@ -3869,11 +3881,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>46.04583740234375</v>
+        <v>46.04584503173828</v>
       </c>
       <c r="C139" t="n">
         <v>46.48400115966797</v>
@@ -3894,7 +3906,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3919,11 +3931,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>47.31179809570312</v>
+        <v>47.31180191040039</v>
       </c>
       <c r="C141" t="n">
         <v>47.76200103759766</v>
@@ -3944,7 +3956,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -3969,11 +3981,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>51.16513442993164</v>
+        <v>51.16513061523438</v>
       </c>
       <c r="C143" t="n">
         <v>51.65200042724609</v>
@@ -3994,11 +4006,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>51.32014846801758</v>
+        <v>51.32015991210938</v>
       </c>
       <c r="C144" t="n">
         <v>51.80849838256836</v>
@@ -4019,11 +4031,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>52.17353057861328</v>
+        <v>52.17353439331055</v>
       </c>
       <c r="C145" t="n">
         <v>52.66999816894531</v>
@@ -4044,7 +4056,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4069,7 +4081,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4094,7 +4106,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4119,11 +4131,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>50.44894409179688</v>
+        <v>50.44894027709961</v>
       </c>
       <c r="C149" t="n">
         <v>50.92900085449219</v>
@@ -4144,7 +4156,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4169,11 +4181,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>55.92730712890625</v>
+        <v>55.92731094360352</v>
       </c>
       <c r="C151" t="n">
         <v>56.45949935913086</v>
@@ -4194,11 +4206,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>60.78261184692383</v>
+        <v>60.78260803222656</v>
       </c>
       <c r="C152" t="n">
         <v>61.36100006103516</v>
@@ -4219,11 +4231,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>61.00945281982422</v>
+        <v>61.00946044921875</v>
       </c>
       <c r="C153" t="n">
         <v>61.59000015258789</v>
@@ -4244,11 +4256,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>59.78511047363281</v>
+        <v>59.78510284423828</v>
       </c>
       <c r="C154" t="n">
         <v>60.35400009155273</v>
@@ -4269,11 +4281,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>54.01501083374023</v>
+        <v>54.0150032043457</v>
       </c>
       <c r="C155" t="n">
         <v>54.52899932861328</v>
@@ -4294,11 +4306,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>54.95951461791992</v>
+        <v>54.95952224731445</v>
       </c>
       <c r="C156" t="n">
         <v>55.48249816894531</v>
@@ -4319,7 +4331,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4344,11 +4356,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>55.76387023925781</v>
+        <v>55.76386642456055</v>
       </c>
       <c r="C158" t="n">
         <v>56.29449844360352</v>
@@ -4369,7 +4381,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4398,11 +4410,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>58.28983306884766</v>
+        <v>58.28982543945312</v>
       </c>
       <c r="C160" t="n">
         <v>58.84450149536133</v>
@@ -4427,7 +4439,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4456,11 +4468,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>54.80351638793945</v>
+        <v>54.80350494384766</v>
       </c>
       <c r="C162" t="n">
         <v>55.32500076293945</v>
@@ -4485,11 +4497,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>53.62967681884766</v>
+        <v>53.62967300415039</v>
       </c>
       <c r="C163" t="n">
         <v>54.13999938964844</v>
@@ -4514,11 +4526,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>60.33586502075195</v>
+        <v>60.33586883544922</v>
       </c>
       <c r="C164" t="n">
         <v>60.90999984741211</v>
@@ -4543,7 +4555,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4572,11 +4584,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>60.48147583007812</v>
+        <v>60.48147201538086</v>
       </c>
       <c r="C166" t="n">
         <v>61.05699920654297</v>
@@ -4601,11 +4613,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>62.34672546386719</v>
+        <v>62.34672927856445</v>
       </c>
       <c r="C167" t="n">
         <v>62.93999862670898</v>
@@ -4630,11 +4642,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>64.58987426757812</v>
+        <v>64.58988189697266</v>
       </c>
       <c r="C168" t="n">
         <v>65.20449829101562</v>
@@ -4659,7 +4671,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4688,7 +4700,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4717,11 +4729,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>66.33131408691406</v>
+        <v>66.33132171630859</v>
       </c>
       <c r="C171" t="n">
         <v>66.96250152587891</v>
@@ -4746,11 +4758,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>57.54987335205078</v>
+        <v>57.54987716674805</v>
       </c>
       <c r="C172" t="n">
         <v>58.09749984741211</v>
@@ -4775,11 +4787,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>66.70030975341797</v>
+        <v>66.70029449462891</v>
       </c>
       <c r="C173" t="n">
         <v>67.33499908447266</v>
@@ -4804,7 +4816,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4833,11 +4845,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>70.23415374755859</v>
+        <v>70.23416137695312</v>
       </c>
       <c r="C175" t="n">
         <v>70.90249633789062</v>
@@ -4862,11 +4874,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>73.69624328613281</v>
+        <v>73.69623565673828</v>
       </c>
       <c r="C176" t="n">
         <v>74.39749908447266</v>
@@ -4891,11 +4903,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>80.70851135253906</v>
+        <v>80.70851898193359</v>
       </c>
       <c r="C177" t="n">
         <v>81.47650146484375</v>
@@ -4920,11 +4932,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>72.58926391601562</v>
+        <v>72.58925628662109</v>
       </c>
       <c r="C178" t="n">
         <v>73.27999877929688</v>
@@ -4949,11 +4961,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>80.04380798339844</v>
+        <v>80.04381561279297</v>
       </c>
       <c r="C179" t="n">
         <v>80.80549621582031</v>
@@ -4978,11 +4990,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>86.89315795898438</v>
+        <v>86.89316558837891</v>
       </c>
       <c r="C180" t="n">
         <v>87.72000122070312</v>
@@ -5007,11 +5019,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>86.80599212646484</v>
+        <v>86.80598449707031</v>
       </c>
       <c r="C181" t="n">
         <v>87.63200378417969</v>
@@ -5036,7 +5048,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5065,11 +5077,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>100.1425628662109</v>
+        <v>100.1425704956055</v>
       </c>
       <c r="C183" t="n">
         <v>101.0954971313477</v>
@@ -5094,11 +5106,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>102.153938293457</v>
+        <v>102.1539306640625</v>
       </c>
       <c r="C184" t="n">
         <v>103.1259994506836</v>
@@ -5123,11 +5135,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>116.565788269043</v>
+        <v>116.565803527832</v>
       </c>
       <c r="C185" t="n">
         <v>117.6750030517578</v>
@@ -5152,7 +5164,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5181,11 +5193,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>120.9386825561523</v>
+        <v>120.9386749267578</v>
       </c>
       <c r="C187" t="n">
         <v>122.0895004272461</v>
@@ -5210,11 +5222,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>133.45654296875</v>
+        <v>133.4565734863281</v>
       </c>
       <c r="C188" t="n">
         <v>134.7265014648438</v>
@@ -5239,11 +5251,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>143.3335723876953</v>
+        <v>143.3335876464844</v>
       </c>
       <c r="C189" t="n">
         <v>144.6974945068359</v>
@@ -5268,11 +5280,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>132.4159393310547</v>
+        <v>132.4159545898438</v>
       </c>
       <c r="C190" t="n">
         <v>133.6759948730469</v>
@@ -5297,11 +5309,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>146.6505432128906</v>
+        <v>146.6504974365234</v>
       </c>
       <c r="C191" t="n">
         <v>148.0460052490234</v>
@@ -5326,11 +5338,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>140.5599822998047</v>
+        <v>140.5599670410156</v>
       </c>
       <c r="C192" t="n">
         <v>141.8975067138672</v>
@@ -5355,11 +5367,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>143.4866180419922</v>
+        <v>143.4866333007812</v>
       </c>
       <c r="C193" t="n">
         <v>144.8520050048828</v>
@@ -5384,7 +5396,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5413,11 +5425,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>133.7839660644531</v>
+        <v>133.7839508056641</v>
       </c>
       <c r="C195" t="n">
         <v>135.0570068359375</v>
@@ -5442,11 +5454,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>137.7566375732422</v>
+        <v>137.7566528320312</v>
       </c>
       <c r="C196" t="n">
         <v>139.0675048828125</v>
@@ -5471,7 +5483,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5500,11 +5512,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>112.6896820068359</v>
+        <v>112.6896743774414</v>
       </c>
       <c r="C198" t="n">
         <v>113.7620010375977</v>
@@ -5529,11 +5541,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>107.935920715332</v>
+        <v>107.9359130859375</v>
       </c>
       <c r="C199" t="n">
         <v>108.9629974365234</v>
@@ -5558,11 +5570,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>115.2235565185547</v>
+        <v>115.2235794067383</v>
       </c>
       <c r="C200" t="n">
         <v>116.3199996948242</v>
@@ -5587,7 +5599,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5616,11 +5628,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>94.74839782714844</v>
+        <v>94.74840545654297</v>
       </c>
       <c r="C202" t="n">
         <v>95.65000152587891</v>
@@ -5645,11 +5657,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>93.619140625</v>
+        <v>93.61914825439453</v>
       </c>
       <c r="C203" t="n">
         <v>94.51000213623047</v>
@@ -5674,11 +5686,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>100.0380783081055</v>
+        <v>100.0380706787109</v>
       </c>
       <c r="C204" t="n">
         <v>100.9899978637695</v>
@@ -5703,11 +5715,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>87.39836120605469</v>
+        <v>87.39834594726562</v>
       </c>
       <c r="C205" t="n">
         <v>88.23000335693359</v>
@@ -5732,11 +5744,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>97.9083251953125</v>
+        <v>97.90834045410156</v>
       </c>
       <c r="C206" t="n">
         <v>98.83999633789062</v>
@@ -5761,7 +5773,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5790,7 +5802,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5819,11 +5831,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>106.3282165527344</v>
+        <v>106.3282089233398</v>
       </c>
       <c r="C209" t="n">
         <v>107.3399963378906</v>
@@ -5848,7 +5860,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5877,11 +5889,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>118.5717010498047</v>
+        <v>118.5717086791992</v>
       </c>
       <c r="C211" t="n">
         <v>119.6999969482422</v>
@@ -5906,11 +5918,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>131.468994140625</v>
+        <v>131.4689636230469</v>
       </c>
       <c r="C212" t="n">
         <v>132.7200012207031</v>
@@ -5935,11 +5947,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>134.8864440917969</v>
+        <v>134.886474609375</v>
       </c>
       <c r="C213" t="n">
         <v>136.1699981689453</v>
@@ -5964,11 +5976,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>129.6264953613281</v>
+        <v>129.6265258789062</v>
       </c>
       <c r="C214" t="n">
         <v>130.8600006103516</v>
@@ -5993,11 +6005,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>122.9104232788086</v>
+        <v>122.9104309082031</v>
       </c>
       <c r="C215" t="n">
         <v>124.0800018310547</v>
@@ -6022,7 +6034,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6051,7 +6063,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6080,7 +6092,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6109,7 +6121,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6138,11 +6150,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>149.50732421875</v>
+        <v>149.5073394775391</v>
       </c>
       <c r="C220" t="n">
         <v>150.9299926757812</v>
@@ -6167,11 +6179,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>161.2456665039062</v>
+        <v>161.2456359863281</v>
       </c>
       <c r="C221" t="n">
         <v>162.7799987792969</v>
@@ -6196,11 +6208,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>170.8740234375</v>
+        <v>170.8740081787109</v>
       </c>
       <c r="C222" t="n">
         <v>172.5</v>
@@ -6225,11 +6237,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>180.6401214599609</v>
+        <v>180.64013671875</v>
       </c>
       <c r="C223" t="n">
         <v>182.1499938964844</v>
@@ -6254,11 +6266,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>170.1180572509766</v>
+        <v>170.1181030273438</v>
       </c>
       <c r="C224" t="n">
         <v>171.5399932861328</v>
@@ -6283,7 +6295,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6312,7 +6324,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6341,11 +6353,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>169.9168395996094</v>
+        <v>169.9168243408203</v>
       </c>
       <c r="C227" t="n">
         <v>171.1100006103516</v>
@@ -6370,11 +6382,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>167.7718811035156</v>
+        <v>167.7718963623047</v>
       </c>
       <c r="C228" t="n">
         <v>168.9499969482422</v>
@@ -6399,7 +6411,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6428,11 +6440,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>202.8295135498047</v>
+        <v>202.8295288085938</v>
       </c>
       <c r="C230" t="n">
         <v>204.0200042724609</v>
@@ -6457,11 +6469,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>169.2863922119141</v>
+        <v>169.2864074707031</v>
       </c>
       <c r="C231" t="n">
         <v>170.2799987792969</v>
@@ -6486,7 +6498,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6515,11 +6527,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>158.0552215576172</v>
+        <v>158.0552062988281</v>
       </c>
       <c r="C233" t="n">
         <v>158.8000030517578</v>
@@ -6544,7 +6556,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6573,7 +6585,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6602,11 +6614,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>191.2311859130859</v>
+        <v>191.2311706542969</v>
       </c>
       <c r="C236" t="n">
         <v>191.8999938964844</v>
@@ -6631,7 +6643,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6660,7 +6672,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6689,11 +6701,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>280.4606018066406</v>
+        <v>280.4606323242188</v>
       </c>
       <c r="C239" t="n">
         <v>281.1900024414062</v>
@@ -6718,7 +6730,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6747,7 +6759,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6776,11 +6788,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>337.3437805175781</v>
+        <v>337.34375</v>
       </c>
       <c r="C242" t="n">
         <v>338</v>
@@ -6805,11 +6817,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>311.1547241210938</v>
+        <v>311.1547546386719</v>
       </c>
       <c r="C243" t="n">
         <v>311.760009765625</v>
@@ -6834,7 +6846,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6863,7 +6875,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6892,7 +6904,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6921,7 +6933,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6950,7 +6962,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -6979,7 +6991,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7008,32 +7020,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>337.8299865722656</v>
+        <v>342.3599853515625</v>
       </c>
       <c r="C250" t="n">
-        <v>337.8299865722656</v>
+        <v>342.3599853515625</v>
       </c>
       <c r="D250" t="n">
-        <v>433515300</v>
+        <v>457374700</v>
       </c>
       <c r="E250" t="n">
         <v>19.91</v>
       </c>
       <c r="F250" t="n">
-        <v>16.9678546746492</v>
+        <v>17.19537847069626</v>
       </c>
       <c r="G250" t="n">
         <v>12230000000</v>
       </c>
       <c r="H250" t="n">
-        <v>4131660735778.809</v>
+        <v>4187062620849.609</v>
       </c>
       <c r="I250" t="n">
-        <v>0.03544687653311529</v>
+        <v>0.03739776778413736</v>
       </c>
     </row>
   </sheetData>
@@ -7065,75 +7077,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7169,13 +7181,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40121</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7211,13 +7223,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7253,13 +7265,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7295,13 +7307,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40121</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7337,13 +7349,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7379,13 +7391,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7421,13 +7433,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7463,13 +7475,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40585</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7496,7 +7508,7 @@
       <c r="I10" t="n">
         <v>0.6584084084084083</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40585</v>
       </c>
       <c r="K10" t="n">
@@ -7509,13 +7521,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7542,7 +7554,7 @@
       <c r="I11" t="n">
         <v>0.6446446446446445</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="K11" t="n">
@@ -7555,13 +7567,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7588,7 +7600,7 @@
       <c r="I12" t="n">
         <v>0.6939439439439438</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="K12" t="n">
@@ -7601,13 +7613,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7634,7 +7646,7 @@
       <c r="I13" t="n">
         <v>0.7342342342342342</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="K13" t="n">
@@ -7647,13 +7659,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40934</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7680,7 +7692,7 @@
       <c r="I14" t="n">
         <v>0.7447447447447447</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40934</v>
       </c>
       <c r="K14" t="n">
@@ -7693,13 +7705,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7726,7 +7738,7 @@
       <c r="I15" t="n">
         <v>0.8258258258258259</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="K15" t="n">
@@ -7739,13 +7751,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41114</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7772,7 +7784,7 @@
       <c r="I16" t="n">
         <v>0.8443443443443444</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41114</v>
       </c>
       <c r="K16" t="n">
@@ -7785,13 +7797,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41082</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7818,7 +7830,7 @@
       <c r="I17" t="n">
         <v>0.7992992992992993</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="K17" t="n">
@@ -7831,13 +7843,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41303</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7864,7 +7876,7 @@
       <c r="I18" t="n">
         <v>0.8085585585585586</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41303</v>
       </c>
       <c r="K18" t="n">
@@ -7877,13 +7889,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7910,7 +7922,7 @@
       <c r="I19" t="n">
         <v>0.8383383383383384</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="K19" t="n">
@@ -7923,13 +7935,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7956,7 +7968,7 @@
       <c r="I20" t="n">
         <v>0.8663663663663664</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="K20" t="n">
@@ -7969,13 +7981,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8002,7 +8014,7 @@
       <c r="I21" t="n">
         <v>0.9219219219219219</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="K21" t="n">
@@ -8015,13 +8027,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41682</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8048,7 +8060,7 @@
       <c r="I22" t="n">
         <v>0.9542042042042043</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41682</v>
       </c>
       <c r="K22" t="n">
@@ -8061,13 +8073,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8094,7 +8106,7 @@
       <c r="I23" t="n">
         <v>0.9574554554554555</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="K23" t="n">
@@ -8107,13 +8119,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8140,7 +8152,7 @@
       <c r="I24" t="n">
         <v>0.9682167167167168</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="K24" t="n">
@@ -8153,13 +8165,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8186,7 +8198,7 @@
       <c r="I25" t="n">
         <v>0.953747747747748</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="K25" t="n">
@@ -8199,13 +8211,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42044</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8232,7 +8244,7 @@
       <c r="I26" t="n">
         <v>1.051</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42044</v>
       </c>
       <c r="K26" t="n">
@@ -8245,13 +8257,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8278,7 +8290,7 @@
       <c r="I27" t="n">
         <v>1.059</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="K27" t="n">
@@ -8291,13 +8303,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8333,13 +8345,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8375,13 +8387,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8417,13 +8429,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8450,7 +8462,7 @@
       <c r="I31" t="n">
         <v>1.3925</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="K31" t="n">
@@ -8463,13 +8475,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8496,7 +8508,7 @@
       <c r="I32" t="n">
         <v>1.478</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="K32" t="n">
@@ -8509,13 +8521,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8542,7 +8554,7 @@
       <c r="I33" t="n">
         <v>1.3785</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="K33" t="n">
@@ -8555,13 +8567,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8588,7 +8600,7 @@
       <c r="I34" t="n">
         <v>1.4945</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="K34" t="n">
@@ -8601,13 +8613,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8634,7 +8646,7 @@
       <c r="I35" t="n">
         <v>0.9</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="K35" t="n">
@@ -8647,13 +8659,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8680,7 +8692,7 @@
       <c r="I36" t="n">
         <v>1.18</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="K36" t="n">
@@ -8693,13 +8705,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43305</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8726,7 +8738,7 @@
       <c r="I37" t="n">
         <v>1.1565</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="K37" t="n">
@@ -8739,13 +8751,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8772,7 +8784,7 @@
       <c r="I38" t="n">
         <v>1.331</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="K38" t="n">
@@ -8785,13 +8797,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8818,7 +8830,7 @@
       <c r="I39" t="n">
         <v>2.185</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="K39" t="n">
@@ -8831,13 +8843,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8864,7 +8876,7 @@
       <c r="I40" t="n">
         <v>1.9935</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K40" t="n">
@@ -8877,13 +8889,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8910,7 +8922,7 @@
       <c r="I41" t="n">
         <v>2.477</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K41" t="n">
@@ -8923,13 +8935,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8956,7 +8968,7 @@
       <c r="I42" t="n">
         <v>2.33</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="K42" t="n">
@@ -8969,13 +8981,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9002,7 +9014,7 @@
       <c r="I43" t="n">
         <v>2.458</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="K43" t="n">
@@ -9015,13 +9027,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9048,7 +9060,7 @@
       <c r="I44" t="n">
         <v>2.4765</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K44" t="n">
@@ -9061,13 +9073,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9094,7 +9106,7 @@
       <c r="I45" t="n">
         <v>2.2725</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K45" t="n">
@@ -9107,13 +9119,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9140,7 +9152,7 @@
       <c r="I46" t="n">
         <v>2.5865</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K46" t="n">
@@ -9153,13 +9165,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44230</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9186,7 +9198,7 @@
       <c r="I47" t="n">
         <v>2.9305</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44230</v>
       </c>
       <c r="K47" t="n">
@@ -9199,13 +9211,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9232,7 +9244,7 @@
       <c r="I48" t="n">
         <v>3.7515</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="K48" t="n">
@@ -9245,13 +9257,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9278,7 +9290,7 @@
       <c r="I49" t="n">
         <v>4.608000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="K49" t="n">
@@ -9291,13 +9303,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9324,7 +9336,7 @@
       <c r="I50" t="n">
         <v>5.1875</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="K50" t="n">
@@ -9337,13 +9349,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9370,7 +9382,7 @@
       <c r="I51" t="n">
         <v>5.61</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="K51" t="n">
@@ -9383,13 +9395,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9416,7 +9428,7 @@
       <c r="I52" t="n">
         <v>5.5265</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="K52" t="n">
@@ -9429,13 +9441,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9462,7 +9474,7 @@
       <c r="I53" t="n">
         <v>5.373500000000001</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="K53" t="n">
@@ -9475,13 +9487,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9508,7 +9520,7 @@
       <c r="I54" t="n">
         <v>5.034000000000001</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="K54" t="n">
@@ -9521,13 +9533,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9554,7 +9566,7 @@
       <c r="I55" t="n">
         <v>4.56</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="K55" t="n">
@@ -9567,13 +9579,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9600,7 +9612,7 @@
       <c r="I56" t="n">
         <v>4.499</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="K56" t="n">
@@ -9613,13 +9625,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9646,7 +9658,7 @@
       <c r="I57" t="n">
         <v>4.728999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="K57" t="n">
@@ -9659,13 +9671,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9692,7 +9704,7 @@
       <c r="I58" t="n">
         <v>5.218999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="K58" t="n">
@@ -9705,13 +9717,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9738,7 +9750,7 @@
       <c r="I59" t="n">
         <v>5.8</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="K59" t="n">
@@ -9751,13 +9763,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9784,7 +9796,7 @@
       <c r="I60" t="n">
         <v>6.52</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="K60" t="n">
@@ -9797,13 +9809,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9830,7 +9842,7 @@
       <c r="I61" t="n">
         <v>6.97</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="K61" t="n">
@@ -9843,13 +9855,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9876,7 +9888,7 @@
       <c r="I62" t="n">
         <v>7.54</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K62" t="n">
@@ -9889,13 +9901,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9922,7 +9934,7 @@
       <c r="I63" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="K63" t="n">
@@ -9935,13 +9947,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9968,7 +9980,7 @@
       <c r="I64" t="n">
         <v>8.959999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="K64" t="n">
@@ -9981,13 +9993,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10014,7 +10026,7 @@
       <c r="I65" t="n">
         <v>9.379999999999999</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="K65" t="n">
@@ -10027,13 +10039,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10060,7 +10072,7 @@
       <c r="I66" t="n">
         <v>10.13</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K66" t="n">
@@ -10073,13 +10085,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46058</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10106,7 +10118,7 @@
       <c r="I67" t="n">
         <v>10.81</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46058</v>
       </c>
       <c r="K67" t="n">
@@ -10119,13 +10131,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10152,7 +10164,7 @@
       <c r="I68" t="n">
         <v>13.11</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K68" t="n">
@@ -10165,13 +10177,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10198,7 +10210,7 @@
       <c r="I69" t="n">
         <v>19.91</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="K69" t="n">
@@ -10236,57 +10248,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="C2" t="n">
@@ -10316,10 +10328,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="C3" t="n">
@@ -10349,10 +10361,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40121</v>
       </c>
       <c r="C4" t="n">
@@ -10382,10 +10394,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40221</v>
       </c>
       <c r="C5" t="n">
@@ -10415,10 +10427,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="C6" t="n">
@@ -10448,10 +10460,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="C7" t="n">
@@ -10481,10 +10493,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="C8" t="n">
@@ -10514,10 +10526,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40585</v>
       </c>
       <c r="C9" t="n">
@@ -10547,10 +10559,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="C10" t="n">
@@ -10580,10 +10592,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="C11" t="n">
@@ -10613,10 +10625,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="C12" t="n">
@@ -10646,10 +10658,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40934</v>
       </c>
       <c r="C13" t="n">
@@ -10679,10 +10691,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="C14" t="n">
@@ -10712,10 +10724,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41114</v>
       </c>
       <c r="C15" t="n">
@@ -10745,10 +10757,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="C16" t="n">
@@ -10778,10 +10790,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41303</v>
       </c>
       <c r="C17" t="n">
@@ -10811,10 +10823,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="C18" t="n">
@@ -10844,10 +10856,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="C19" t="n">
@@ -10877,10 +10889,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="C20" t="n">
@@ -10910,10 +10922,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41682</v>
       </c>
       <c r="C21" t="n">
@@ -10943,10 +10955,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="C22" t="n">
@@ -10976,10 +10988,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="C23" t="n">
@@ -11013,10 +11025,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42044</v>
       </c>
       <c r="C24" t="n">
@@ -11050,10 +11062,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42044</v>
       </c>
       <c r="C25" t="n">
@@ -11087,10 +11099,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42044</v>
       </c>
       <c r="C26" t="n">
@@ -11124,10 +11136,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="C27" t="n">
@@ -11161,10 +11173,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="C28" t="n">
@@ -11194,10 +11206,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="C29" t="n">
@@ -11227,10 +11239,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="C30" t="n">
@@ -11260,10 +11272,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C31" t="n">
@@ -11293,10 +11305,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C32" t="n">
@@ -11326,10 +11338,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="C33" t="n">
@@ -11359,10 +11371,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="C34" t="n">
@@ -11392,10 +11404,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="C35" t="n">
@@ -11425,10 +11437,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C36" t="n">
@@ -11458,10 +11470,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43137</v>
       </c>
       <c r="C37" t="n">
@@ -11491,10 +11503,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="C38" t="n">
@@ -11524,10 +11536,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43305</v>
       </c>
       <c r="C39" t="n">
@@ -11557,10 +11569,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C40" t="n">
@@ -11590,10 +11602,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="C41" t="n">
@@ -11623,10 +11635,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C42" t="n">
@@ -11656,10 +11668,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C43" t="n">
@@ -11689,10 +11701,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="C44" t="n">
@@ -11722,10 +11734,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="C45" t="n">
@@ -11755,10 +11767,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C46" t="n">
@@ -11788,10 +11800,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C47" t="n">
@@ -11821,10 +11833,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C48" t="n">
@@ -11854,10 +11866,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44230</v>
       </c>
       <c r="C49" t="n">
@@ -11887,10 +11899,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="C50" t="n">
@@ -11920,10 +11932,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="C51" t="n">
@@ -11953,10 +11965,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="C52" t="n">
@@ -11986,10 +11998,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="C53" t="n">
@@ -12019,10 +12031,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="C54" t="n">
@@ -12052,10 +12064,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="C55" t="n">
@@ -12085,10 +12097,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="C56" t="n">
@@ -12118,10 +12130,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="C57" t="n">
@@ -12151,10 +12163,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="C58" t="n">
@@ -12184,10 +12196,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="C59" t="n">
@@ -12217,10 +12229,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="C60" t="n">
@@ -12250,10 +12262,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="C61" t="n">
@@ -12283,10 +12295,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="C62" t="n">
@@ -12316,10 +12328,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="C63" t="n">
@@ -12349,10 +12361,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C64" t="n">
@@ -12382,10 +12394,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="C65" t="n">
@@ -12415,10 +12427,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="C66" t="n">
@@ -12448,10 +12460,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="C67" t="n">
@@ -12481,10 +12493,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C68" t="n">
@@ -12514,10 +12526,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46058</v>
       </c>
       <c r="C69" t="n">
@@ -12547,10 +12559,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C70" t="n">
@@ -12580,10 +12592,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="C71" t="n">
@@ -12631,12 +12643,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/GOOGL.xlsx
+++ b/salidas/empresas/GOOGL.xlsx
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>8.989039421081543</v>
+        <v>8.989038467407227</v>
       </c>
       <c r="C3" t="n">
         <v>9.074575424194336</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>10.36037349700928</v>
+        <v>10.36037254333496</v>
       </c>
       <c r="C5" t="n">
         <v>10.45895862579346</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>9.217098236083984</v>
+        <v>9.217097282409668</v>
       </c>
       <c r="C6" t="n">
         <v>9.304804801940918</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>9.962754249572754</v>
+        <v>9.96275520324707</v>
       </c>
       <c r="C10" t="n">
         <v>10.05755805969238</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>11.41490364074707</v>
+        <v>11.41490268707275</v>
       </c>
       <c r="C13" t="n">
         <v>11.52352428436279</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.43175315856934</v>
+        <v>12.43175220489502</v>
       </c>
       <c r="C14" t="n">
         <v>12.55004978179932</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>11.35739231109619</v>
+        <v>11.35739326477051</v>
       </c>
       <c r="C16" t="n">
         <v>11.46546459197998</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>12.3427619934082</v>
+        <v>12.34276008605957</v>
       </c>
       <c r="C18" t="n">
         <v>12.46020984649658</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>12.95728397369385</v>
+        <v>12.95728302001953</v>
       </c>
       <c r="C19" t="n">
         <v>13.08058071136475</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>12.64245986938477</v>
+        <v>12.64246082305908</v>
       </c>
       <c r="C20" t="n">
         <v>12.76276302337646</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>12.77260398864746</v>
+        <v>12.77260303497314</v>
       </c>
       <c r="C21" t="n">
         <v>12.89414405822754</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>17.52592468261719</v>
+        <v>17.52592277526855</v>
       </c>
       <c r="C23" t="n">
         <v>17.69269371032715</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>13.98851013183594</v>
+        <v>13.98851108551025</v>
       </c>
       <c r="C26" t="n">
         <v>14.12162208557129</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>11.68014526367188</v>
+        <v>11.68014621734619</v>
       </c>
       <c r="C27" t="n">
         <v>11.79129123687744</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>10.91887187957764</v>
+        <v>10.91887092590332</v>
       </c>
       <c r="C28" t="n">
         <v>11.02277278900146</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>14.23615646362305</v>
+        <v>14.23615550994873</v>
       </c>
       <c r="C29" t="n">
         <v>14.37162208557129</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>11.48456001281738</v>
+        <v>11.48455905914307</v>
       </c>
       <c r="C33" t="n">
         <v>11.59384441375732</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>9.928545951843262</v>
+        <v>9.928544998168945</v>
       </c>
       <c r="C34" t="n">
         <v>10.02302265167236</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>8.908226013183594</v>
+        <v>8.908225059509277</v>
       </c>
       <c r="C35" t="n">
         <v>8.992993354797363</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>8.628108024597168</v>
+        <v>8.628107070922852</v>
       </c>
       <c r="C40" t="n">
         <v>8.710209846496582</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>10.98282814025879</v>
+        <v>10.98282623291016</v>
       </c>
       <c r="C44" t="n">
         <v>11.08733654022217</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>11.4443998336792</v>
+        <v>11.44440078735352</v>
       </c>
       <c r="C45" t="n">
         <v>11.55330276489258</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>12.29169654846191</v>
+        <v>12.29169464111328</v>
       </c>
       <c r="C46" t="n">
         <v>12.40865898132324</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>13.28995323181152</v>
+        <v>13.28995418548584</v>
       </c>
       <c r="C47" t="n">
         <v>13.41641616821289</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>14.45206832885742</v>
+        <v>14.45206737518311</v>
       </c>
       <c r="C48" t="n">
         <v>14.58959007263184</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>15.36877059936523</v>
+        <v>15.36877155303955</v>
       </c>
       <c r="C49" t="n">
         <v>15.5150146484375</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>13.13675689697266</v>
+        <v>13.13675594329834</v>
       </c>
       <c r="C50" t="n">
         <v>13.26176166534424</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>13.05891799926758</v>
+        <v>13.05891895294189</v>
       </c>
       <c r="C51" t="n">
         <v>13.18318271636963</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>13.03165149688721</v>
+        <v>13.03165054321289</v>
       </c>
       <c r="C53" t="n">
         <v>13.15565586090088</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>12.03834819793701</v>
+        <v>12.03835010528564</v>
       </c>
       <c r="C54" t="n">
         <v>12.15290260314941</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>11.02992630004883</v>
+        <v>11.02992725372314</v>
       </c>
       <c r="C55" t="n">
         <v>11.13488483428955</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>12.01901435852051</v>
+        <v>12.01901340484619</v>
       </c>
       <c r="C56" t="n">
         <v>12.13338279724121</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>11.15560913085938</v>
+        <v>11.15560817718506</v>
       </c>
       <c r="C57" t="n">
         <v>11.26176166534424</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>13.77557468414307</v>
+        <v>13.77557373046875</v>
       </c>
       <c r="C60" t="n">
         <v>13.90665721893311</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>14.72400569915771</v>
+        <v>14.7240047454834</v>
       </c>
       <c r="C61" t="n">
         <v>14.86411380767822</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>14.54527568817139</v>
+        <v>14.54527473449707</v>
       </c>
       <c r="C64" t="n">
         <v>14.68368434906006</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>12.76739883422852</v>
+        <v>12.76739978790283</v>
       </c>
       <c r="C70" t="n">
         <v>12.88888931274414</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>14.69103622436523</v>
+        <v>14.69103527069092</v>
       </c>
       <c r="C71" t="n">
         <v>14.83083057403564</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>14.85836219787598</v>
+        <v>14.85836315155029</v>
       </c>
       <c r="C72" t="n">
         <v>14.9997501373291</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>16.01130485534668</v>
+        <v>16.01130676269531</v>
       </c>
       <c r="C73" t="n">
         <v>16.16366386413574</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>14.38042736053467</v>
+        <v>14.38042831420898</v>
       </c>
       <c r="C74" t="n">
         <v>14.51726722717285</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>15.89578723907471</v>
+        <v>15.89578819274902</v>
       </c>
       <c r="C76" t="n">
         <v>16.04704666137695</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>14.99371147155762</v>
+        <v>14.9937105178833</v>
       </c>
       <c r="C77" t="n">
         <v>15.13638591766357</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>15.69078159332275</v>
+        <v>15.69078063964844</v>
       </c>
       <c r="C80" t="n">
         <v>15.84008979797363</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>18.70340538024902</v>
+        <v>18.70340347290039</v>
       </c>
       <c r="C82" t="n">
         <v>18.88138008117676</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>16.86405181884766</v>
+        <v>16.86405372619629</v>
       </c>
       <c r="C83" t="n">
         <v>17.0245246887207</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>18.7329044342041</v>
+        <v>18.73290634155273</v>
       </c>
       <c r="C86" t="n">
         <v>18.91116142272949</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>19.68728637695312</v>
+        <v>19.68728828430176</v>
       </c>
       <c r="C88" t="n">
         <v>19.87462425231934</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>20.44038200378418</v>
+        <v>20.44037818908691</v>
       </c>
       <c r="C89" t="n">
         <v>20.63488578796387</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>21.82361793518066</v>
+        <v>21.8236141204834</v>
       </c>
       <c r="C91" t="n">
         <v>22.03128051757812</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>22.00655746459961</v>
+        <v>22.00655555725098</v>
       </c>
       <c r="C92" t="n">
         <v>22.21596527099609</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>21.71305465698242</v>
+        <v>21.71305847167969</v>
       </c>
       <c r="C94" t="n">
         <v>21.91967010498047</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>30.13492012023926</v>
+        <v>30.13491821289062</v>
       </c>
       <c r="C99" t="n">
         <v>30.42167282104492</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>27.62774085998535</v>
+        <v>27.62774276733398</v>
       </c>
       <c r="C100" t="n">
         <v>27.89064025878906</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>28.95794486999512</v>
+        <v>28.95794296264648</v>
       </c>
       <c r="C103" t="n">
         <v>29.23349952697754</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>28.70435905456543</v>
+        <v>28.7043571472168</v>
       </c>
       <c r="C104" t="n">
         <v>28.97750091552734</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>28.84353446960449</v>
+        <v>28.84353256225586</v>
       </c>
       <c r="C105" t="n">
         <v>29.11800003051758</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>29.14317893981934</v>
+        <v>29.1431827545166</v>
       </c>
       <c r="C106" t="n">
         <v>29.42049980163574</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>27.19522094726562</v>
+        <v>27.19521903991699</v>
       </c>
       <c r="C108" t="n">
         <v>27.45400047302246</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>26.28289985656738</v>
+        <v>26.28290367126465</v>
       </c>
       <c r="C109" t="n">
         <v>26.53300094604492</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>27.8663330078125</v>
+        <v>27.86633110046387</v>
       </c>
       <c r="C111" t="n">
         <v>28.13150024414062</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>27.17986679077148</v>
+        <v>27.17986488342285</v>
       </c>
       <c r="C113" t="n">
         <v>27.43849945068359</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>26.74748039245605</v>
+        <v>26.74748229980469</v>
       </c>
       <c r="C115" t="n">
         <v>27.00200080871582</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>32.56512069702148</v>
+        <v>32.56511688232422</v>
       </c>
       <c r="C116" t="n">
         <v>32.875</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>37.78297805786133</v>
+        <v>37.78297424316406</v>
       </c>
       <c r="C120" t="n">
         <v>38.14250183105469</v>
@@ -3466,7 +3466,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>37.70867156982422</v>
+        <v>37.70867538452148</v>
       </c>
       <c r="C122" t="n">
         <v>38.06750106811523</v>
@@ -3510,7 +3510,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>37.78544616699219</v>
+        <v>37.78544998168945</v>
       </c>
       <c r="C124" t="n">
         <v>38.14500045776367</v>
@@ -3535,7 +3535,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>35.06038284301758</v>
+        <v>35.06037902832031</v>
       </c>
       <c r="C125" t="n">
         <v>35.39400100708008</v>
@@ -3560,7 +3560,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>37.08956909179688</v>
+        <v>37.08957290649414</v>
       </c>
       <c r="C126" t="n">
         <v>37.44250106811523</v>
@@ -3585,7 +3585,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>34.84492111206055</v>
+        <v>34.84492492675781</v>
       </c>
       <c r="C127" t="n">
         <v>35.17649841308594</v>
@@ -3635,7 +3635,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>39.12024688720703</v>
+        <v>39.12024307250977</v>
       </c>
       <c r="C129" t="n">
         <v>39.49250030517578</v>
@@ -3685,7 +3685,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>40.11329650878906</v>
+        <v>40.1132926940918</v>
       </c>
       <c r="C131" t="n">
         <v>40.49499893188477</v>
@@ -3710,7 +3710,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>38.4283332824707</v>
+        <v>38.42832946777344</v>
       </c>
       <c r="C132" t="n">
         <v>38.79399871826172</v>
@@ -3735,7 +3735,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>39.24901962280273</v>
+        <v>39.2490234375</v>
       </c>
       <c r="C133" t="n">
         <v>39.62250137329102</v>
@@ -3785,7 +3785,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>41.8482780456543</v>
+        <v>41.84828186035156</v>
       </c>
       <c r="C135" t="n">
         <v>42.24649810791016</v>
@@ -3860,7 +3860,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>48.88928604125977</v>
+        <v>48.8892822265625</v>
       </c>
       <c r="C138" t="n">
         <v>49.35449981689453</v>
@@ -3885,7 +3885,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>46.04584503173828</v>
+        <v>46.04584121704102</v>
       </c>
       <c r="C139" t="n">
         <v>46.48400115966797</v>
@@ -3910,7 +3910,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>46.82938003540039</v>
+        <v>46.82938385009766</v>
       </c>
       <c r="C140" t="n">
         <v>47.27500152587891</v>
@@ -3935,7 +3935,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>47.31180191040039</v>
+        <v>47.31179809570312</v>
       </c>
       <c r="C141" t="n">
         <v>47.76200103759766</v>
@@ -3960,7 +3960,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>48.22708892822266</v>
+        <v>48.22708511352539</v>
       </c>
       <c r="C142" t="n">
         <v>48.68600082397461</v>
@@ -3985,7 +3985,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>51.16513061523438</v>
+        <v>51.16513442993164</v>
       </c>
       <c r="C143" t="n">
         <v>51.65200042724609</v>
@@ -4035,7 +4035,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>52.17353439331055</v>
+        <v>52.17353057861328</v>
       </c>
       <c r="C145" t="n">
         <v>52.66999816894531</v>
@@ -4060,7 +4060,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>58.5538215637207</v>
+        <v>58.55381774902344</v>
       </c>
       <c r="C146" t="n">
         <v>59.11100006103516</v>
@@ -4085,7 +4085,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>54.67572402954102</v>
+        <v>54.67572784423828</v>
       </c>
       <c r="C147" t="n">
         <v>55.19599914550781</v>
@@ -4110,7 +4110,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>51.36819458007812</v>
+        <v>51.36819076538086</v>
       </c>
       <c r="C148" t="n">
         <v>51.85699844360352</v>
@@ -4135,7 +4135,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>50.44894027709961</v>
+        <v>50.44894409179688</v>
       </c>
       <c r="C149" t="n">
         <v>50.92900085449219</v>
@@ -4160,7 +4160,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>54.4815673828125</v>
+        <v>54.48157119750977</v>
       </c>
       <c r="C150" t="n">
         <v>55</v>
@@ -4210,7 +4210,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>60.78260803222656</v>
+        <v>60.78261184692383</v>
       </c>
       <c r="C152" t="n">
         <v>61.36100006103516</v>
@@ -4285,7 +4285,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>54.0150032043457</v>
+        <v>54.01500701904297</v>
       </c>
       <c r="C155" t="n">
         <v>54.52899932861328</v>
@@ -4310,7 +4310,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>54.95952224731445</v>
+        <v>54.95952606201172</v>
       </c>
       <c r="C156" t="n">
         <v>55.48249816894531</v>
@@ -4360,7 +4360,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>55.76386642456055</v>
+        <v>55.76387023925781</v>
       </c>
       <c r="C158" t="n">
         <v>56.29449844360352</v>
@@ -4385,7 +4385,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>55.79655838012695</v>
+        <v>55.79656219482422</v>
       </c>
       <c r="C159" t="n">
         <v>56.32749938964844</v>
@@ -4414,7 +4414,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>58.28982543945312</v>
+        <v>58.28982925415039</v>
       </c>
       <c r="C160" t="n">
         <v>58.84450149536133</v>
@@ -4443,7 +4443,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>59.38293838500977</v>
+        <v>59.3829345703125</v>
       </c>
       <c r="C161" t="n">
         <v>59.94800186157227</v>
@@ -4472,7 +4472,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>54.80350494384766</v>
+        <v>54.80350875854492</v>
       </c>
       <c r="C162" t="n">
         <v>55.32500076293945</v>
@@ -4501,7 +4501,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>53.62967300415039</v>
+        <v>53.62967681884766</v>
       </c>
       <c r="C163" t="n">
         <v>54.13999938964844</v>
@@ -4530,7 +4530,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>60.33586883544922</v>
+        <v>60.33586502075195</v>
       </c>
       <c r="C164" t="n">
         <v>60.90999984741211</v>
@@ -4617,7 +4617,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>62.34672927856445</v>
+        <v>62.34672546386719</v>
       </c>
       <c r="C167" t="n">
         <v>62.93999862670898</v>
@@ -4675,7 +4675,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>66.33824157714844</v>
+        <v>66.33823394775391</v>
       </c>
       <c r="C169" t="n">
         <v>66.96949768066406</v>
@@ -4733,7 +4733,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>66.33132171630859</v>
+        <v>66.33131408691406</v>
       </c>
       <c r="C171" t="n">
         <v>66.96250152587891</v>
@@ -4791,7 +4791,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>66.70029449462891</v>
+        <v>66.70030975341797</v>
       </c>
       <c r="C173" t="n">
         <v>67.33499908447266</v>
@@ -4849,7 +4849,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>70.23416137695312</v>
+        <v>70.23416900634766</v>
       </c>
       <c r="C175" t="n">
         <v>70.90249633789062</v>
@@ -4878,7 +4878,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>73.69623565673828</v>
+        <v>73.69622802734375</v>
       </c>
       <c r="C176" t="n">
         <v>74.39749908447266</v>
@@ -4907,7 +4907,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>80.70851898193359</v>
+        <v>80.70851135253906</v>
       </c>
       <c r="C177" t="n">
         <v>81.47650146484375</v>
@@ -4965,7 +4965,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>80.04381561279297</v>
+        <v>80.0438232421875</v>
       </c>
       <c r="C179" t="n">
         <v>80.80549621582031</v>
@@ -4994,7 +4994,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>86.89316558837891</v>
+        <v>86.89315795898438</v>
       </c>
       <c r="C180" t="n">
         <v>87.72000122070312</v>
@@ -5052,7 +5052,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>90.50675964355469</v>
+        <v>90.50675201416016</v>
       </c>
       <c r="C182" t="n">
         <v>91.36799621582031</v>
@@ -5139,7 +5139,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>116.565803527832</v>
+        <v>116.565788269043</v>
       </c>
       <c r="C185" t="n">
         <v>117.6750030517578</v>
@@ -5226,7 +5226,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>133.4565734863281</v>
+        <v>133.4565582275391</v>
       </c>
       <c r="C188" t="n">
         <v>134.7265014648438</v>
@@ -5284,7 +5284,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>132.4159545898438</v>
+        <v>132.4159393310547</v>
       </c>
       <c r="C190" t="n">
         <v>133.6759948730469</v>
@@ -5313,7 +5313,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>146.6504974365234</v>
+        <v>146.6504821777344</v>
       </c>
       <c r="C191" t="n">
         <v>148.0460052490234</v>
@@ -5371,7 +5371,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>143.4866333007812</v>
+        <v>143.4866180419922</v>
       </c>
       <c r="C193" t="n">
         <v>144.8520050048828</v>
@@ -5429,7 +5429,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>133.7839508056641</v>
+        <v>133.783935546875</v>
       </c>
       <c r="C195" t="n">
         <v>135.0570068359375</v>
@@ -5458,7 +5458,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>137.7566528320312</v>
+        <v>137.7566680908203</v>
       </c>
       <c r="C196" t="n">
         <v>139.0675048828125</v>
@@ -5487,7 +5487,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>113.0339050292969</v>
+        <v>113.0338973999023</v>
       </c>
       <c r="C197" t="n">
         <v>114.1094970703125</v>
@@ -5545,7 +5545,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>107.9359130859375</v>
+        <v>107.935905456543</v>
       </c>
       <c r="C199" t="n">
         <v>108.9629974365234</v>
@@ -5574,7 +5574,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>115.2235794067383</v>
+        <v>115.2235717773438</v>
       </c>
       <c r="C200" t="n">
         <v>116.3199996948242</v>
@@ -5690,7 +5690,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>100.0380706787109</v>
+        <v>100.0380630493164</v>
       </c>
       <c r="C204" t="n">
         <v>100.9899978637695</v>
@@ -5806,7 +5806,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>102.7522354125977</v>
+        <v>102.7522430419922</v>
       </c>
       <c r="C208" t="n">
         <v>103.7300033569336</v>
@@ -5835,7 +5835,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>106.3282089233398</v>
+        <v>106.3282012939453</v>
       </c>
       <c r="C209" t="n">
         <v>107.3399963378906</v>
@@ -5864,7 +5864,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>121.7118301391602</v>
+        <v>121.7118225097656</v>
       </c>
       <c r="C210" t="n">
         <v>122.870002746582</v>
@@ -5893,7 +5893,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>118.5717086791992</v>
+        <v>118.5717163085938</v>
       </c>
       <c r="C211" t="n">
         <v>119.6999969482422</v>
@@ -5922,7 +5922,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>131.4689636230469</v>
+        <v>131.4689788818359</v>
       </c>
       <c r="C212" t="n">
         <v>132.7200012207031</v>
@@ -5980,7 +5980,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>129.6265258789062</v>
+        <v>129.6265411376953</v>
       </c>
       <c r="C214" t="n">
         <v>130.8600006103516</v>
@@ -6009,7 +6009,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>122.9104309082031</v>
+        <v>122.9104232788086</v>
       </c>
       <c r="C215" t="n">
         <v>124.0800018310547</v>
@@ -6038,7 +6038,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>131.28076171875</v>
+        <v>131.2807464599609</v>
       </c>
       <c r="C216" t="n">
         <v>132.5299987792969</v>
@@ -6067,7 +6067,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>138.3732757568359</v>
+        <v>138.3732604980469</v>
       </c>
       <c r="C217" t="n">
         <v>139.6900024414062</v>
@@ -6096,7 +6096,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>138.7794342041016</v>
+        <v>138.7794036865234</v>
       </c>
       <c r="C218" t="n">
         <v>140.1000061035156</v>
@@ -6125,7 +6125,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>137.1548767089844</v>
+        <v>137.1548919677734</v>
       </c>
       <c r="C219" t="n">
         <v>138.4600067138672</v>
@@ -6212,7 +6212,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>170.8740081787109</v>
+        <v>170.8740234375</v>
       </c>
       <c r="C222" t="n">
         <v>172.5</v>
@@ -6241,7 +6241,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>180.64013671875</v>
+        <v>180.6401214599609</v>
       </c>
       <c r="C223" t="n">
         <v>182.1499938964844</v>
@@ -6270,7 +6270,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>170.1181030273438</v>
+        <v>170.1180725097656</v>
       </c>
       <c r="C224" t="n">
         <v>171.5399932861328</v>
@@ -6328,7 +6328,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>164.6935119628906</v>
+        <v>164.6934967041016</v>
       </c>
       <c r="C226" t="n">
         <v>165.8500061035156</v>
@@ -6386,7 +6386,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>167.7718963623047</v>
+        <v>167.7718811035156</v>
       </c>
       <c r="C228" t="n">
         <v>168.9499969482422</v>
@@ -6444,7 +6444,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>202.8295288085938</v>
+        <v>202.8295440673828</v>
       </c>
       <c r="C230" t="n">
         <v>204.0200042724609</v>
@@ -6473,7 +6473,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>169.2864074707031</v>
+        <v>169.2863922119141</v>
       </c>
       <c r="C231" t="n">
         <v>170.2799987792969</v>
@@ -6502,7 +6502,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>153.9147186279297</v>
+        <v>153.9147033691406</v>
       </c>
       <c r="C232" t="n">
         <v>154.6399993896484</v>
@@ -6589,7 +6589,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>175.6157989501953</v>
+        <v>175.6158142089844</v>
       </c>
       <c r="C235" t="n">
         <v>176.2299957275391</v>
@@ -6618,7 +6618,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>191.2311706542969</v>
+        <v>191.231201171875</v>
       </c>
       <c r="C236" t="n">
         <v>191.8999938964844</v>
@@ -6676,7 +6676,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>242.4694213867188</v>
+        <v>242.4694366455078</v>
       </c>
       <c r="C238" t="n">
         <v>243.1000061035156</v>
@@ -6705,7 +6705,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>280.4606323242188</v>
+        <v>280.4606628417969</v>
       </c>
       <c r="C239" t="n">
         <v>281.1900024414062</v>
@@ -6763,7 +6763,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>312.3923034667969</v>
+        <v>312.392333984375</v>
       </c>
       <c r="C241" t="n">
         <v>313</v>
@@ -6792,7 +6792,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>337.34375</v>
+        <v>337.3437805175781</v>
       </c>
       <c r="C242" t="n">
         <v>338</v>
